--- a/stores picture/雙醬.xlsx
+++ b/stores picture/雙醬.xlsx
@@ -218,7 +218,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>醬汁填在備註</t>
+    <t>奶油,咖哩,雙醬</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="27.81640625" customWidth="1"/>
@@ -735,7 +735,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -743,7 +743,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -751,282 +751,282 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="1">
         <v>70</v>
       </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B20" s="1">
         <v>110</v>
       </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="1">
         <v>120</v>
       </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="1">
         <v>130</v>
       </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="1">
         <v>130</v>
       </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B24" s="1">
         <v>140</v>
       </c>
-      <c r="C24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B25" s="1">
         <v>140</v>
       </c>
-      <c r="C25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="1">
         <v>150</v>
       </c>
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="1">
         <v>150</v>
       </c>
-      <c r="C27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="1">
         <v>120</v>
       </c>
-      <c r="C28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B29" s="1">
         <v>130</v>
       </c>
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B30" s="1">
         <v>140</v>
       </c>
-      <c r="C30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B31" s="1">
         <v>140</v>
       </c>
-      <c r="C31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B32" s="1">
         <v>150</v>
       </c>
-      <c r="C32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="1">
         <v>150</v>
       </c>
-      <c r="C33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B34" s="1">
         <v>160</v>
       </c>
-      <c r="C34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="1">
         <v>160</v>
       </c>
-      <c r="C35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="1">
         <v>120</v>
       </c>
-      <c r="C36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B37" s="1">
         <v>130</v>
       </c>
-      <c r="C37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D37" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="1">
         <v>140</v>
       </c>
-      <c r="C38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="1">
         <v>140</v>
       </c>
-      <c r="C39" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B40" s="1">
         <v>150</v>
       </c>
-      <c r="C40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B41" s="1">
         <v>150</v>
       </c>
-      <c r="C41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B42" s="1">
         <v>160</v>
       </c>
-      <c r="C42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D42" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B43" s="1">
         <v>160</v>
       </c>
-      <c r="C43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>41</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>42</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>43</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>44</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>45</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>46</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>47</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>49</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>51</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>52</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>53</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>54</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>55</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>56</v>
       </c>
@@ -1154,80 +1154,80 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B60" s="1">
         <v>150</v>
       </c>
-      <c r="C60" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B61" s="1">
         <v>170</v>
       </c>
-      <c r="C61" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D61" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B62" s="1">
         <v>180</v>
       </c>
-      <c r="C62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D62" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B63" s="1">
         <v>180</v>
       </c>
-      <c r="C63" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D63" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B64" s="1">
         <v>200</v>
       </c>
-      <c r="C64" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D64" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B65" s="1">
         <v>200</v>
       </c>
-      <c r="C65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D65" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B66" s="1">
         <v>200</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>66</v>
       </c>
     </row>
